--- a/preschool-teaching/output/02 4.2 Penjajaran Jam Latihan CA-CU/4.2_Penjajaran Jam Latihan CA_CU_EU Program ADI Pekerjaan (P851).xlsx
+++ b/preschool-teaching/output/02 4.2 Penjajaran Jam Latihan CA-CU/4.2_Penjajaran Jam Latihan CA_CU_EU Program ADI Pekerjaan (P851).xlsx
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C11" s="6">
-        <f>($B$8-$C$10)/ROWS(A11:A16)</f>
+        <f>($B$8-$C$10)/5</f>
         <v/>
       </c>
       <c r="D11" s="5">
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="C12" s="6">
-        <f>($B$8-$C$10)/ROWS(A12:A17)</f>
+        <f>($B$8-$C$10)/5</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>C12/8</f>
+        <f>$C$12/8</f>
         <v/>
       </c>
       <c r="E12" s="17" t="n">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="C13" s="6">
-        <f>($B$8-$C$10)/ROWS(A13:A18)</f>
+        <f>($B$8-$C$10)/5</f>
         <v/>
       </c>
       <c r="D13" s="5">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C14" s="6">
-        <f>($B$8-$C$10)/ROWS(A14:A19)</f>
+        <f>($B$8-$C$10)/5</f>
         <v/>
       </c>
       <c r="D14" s="5">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="C15" s="6">
-        <f>($B$8-$C$10)/ROWS(A15:A20)</f>
+        <f>($B$8-$C$10)/5</f>
         <v/>
       </c>
       <c r="D15" s="5">
@@ -939,27 +939,11 @@
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1" s="24" thickBot="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>C06</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>Product Marketing</t>
-        </is>
-      </c>
-      <c r="C16" s="6">
-        <f>($B$8-$C$10)/ROWS(A16:A21)</f>
-        <v/>
-      </c>
-      <c r="D16" s="5">
-        <f>$C$16/8</f>
-        <v/>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>10</v>
-      </c>
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="17" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1" s="24" thickBot="1" thickTop="1">
       <c r="A17" s="22" t="inlineStr">
@@ -968,15 +952,16 @@
         </is>
       </c>
       <c r="B17" s="33" t="n"/>
-      <c r="C17" s="8" t="n">
-        <v>576</v>
+      <c r="C17" s="8">
+        <f>SUM(C10:C15)</f>
+        <v/>
       </c>
       <c r="D17" s="22">
-        <f>SUM(D10:D16)</f>
+        <f>SUM(D10:D15)</f>
         <v/>
       </c>
       <c r="E17" s="18">
-        <f>SUM(E10:E16)</f>
+        <f>SUM(E10:E15)</f>
         <v/>
       </c>
     </row>
